--- a/data/trans_orig/Q33-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las horas al día que duerme habitualmente</t>
+          <t>Población según las horas al día que duerme habitualmente (tasa de respuesta: 98,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 8,03</t>
+          <t>7,82; 8,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 7,99</t>
+          <t>7,65; 7,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,88</t>
+          <t>7,65; 7,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,85</t>
+          <t>7,64; 7,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,82</t>
+          <t>7,52; 7,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 7,91</t>
+          <t>7,77; 7,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 7,87</t>
+          <t>7,64; 7,87</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,63</t>
+          <t>7,5; 7,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,48</t>
+          <t>7,26; 7,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,67</t>
+          <t>7,51; 7,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,63</t>
+          <t>7,46; 7,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,38</t>
+          <t>7,14; 7,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,5</t>
+          <t>7,36; 7,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,6</t>
+          <t>7,47; 7,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,41</t>
+          <t>7,22; 7,4</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,5</t>
+          <t>7,32; 7,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,32</t>
+          <t>7,15; 7,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,42</t>
+          <t>7,25; 7,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,24</t>
+          <t>7,06; 7,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,5</t>
+          <t>7,36; 7,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,36</t>
+          <t>7,2; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,18</t>
+          <t>7,03; 7,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,48</t>
+          <t>7,36; 7,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,32</t>
+          <t>7,19; 7,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,37</t>
+          <t>7,26; 7,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,2</t>
+          <t>7,07; 7,2</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,49</t>
+          <t>7,29; 7,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,28</t>
+          <t>7,09; 7,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,32</t>
+          <t>6,98; 8,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,07</t>
+          <t>6,85; 7,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,27 +1171,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,07</t>
+          <t>6,94; 7,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,42</t>
+          <t>7,27; 7,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,14</t>
+          <t>7,0; 7,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,28</t>
+          <t>7,15; 7,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,0</t>
+          <t>6,99; 8,01</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,49</t>
+          <t>7,26; 7,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,34</t>
+          <t>7,1; 7,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,44</t>
+          <t>7,19; 7,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,07</t>
+          <t>6,9; 7,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,03</t>
+          <t>6,76; 7,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,34</t>
+          <t>7,16; 7,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,19</t>
+          <t>7,01; 7,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,81; 6,92</t>
+          <t>6,8; 6,92</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1416,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,62</t>
+          <t>7,33; 7,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,49</t>
+          <t>7,12; 7,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,64</t>
+          <t>7,34; 7,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,03</t>
+          <t>6,83; 7,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,04</t>
+          <t>6,76; 7,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,05</t>
+          <t>6,74; 7,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,13</t>
+          <t>6,83; 7,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 6,84</t>
+          <t>6,22; 6,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,21</t>
+          <t>6,98; 7,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 6,9</t>
+          <t>6,33; 6,89</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,54</t>
+          <t>7,21; 7,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,74</t>
+          <t>7,27; 7,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,22 +1571,22 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,11</t>
+          <t>6,88; 7,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,21</t>
+          <t>6,84; 7,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,18</t>
+          <t>6,85; 7,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,36</t>
+          <t>7,0; 7,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,35</t>
+          <t>7,08; 7,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 7,48</t>
+          <t>7,24; 7,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 6,97</t>
+          <t>6,82; 6,98</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,51</t>
+          <t>7,42; 7,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,69</t>
+          <t>7,15; 7,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,23</t>
+          <t>7,13; 7,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,29</t>
+          <t>7,2; 7,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,05</t>
+          <t>6,78; 7,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,31</t>
+          <t>7,25; 7,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,34</t>
+          <t>7,03; 7,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q33-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Edad-trans_orig.xlsx
@@ -663,47 +663,47 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>7,78</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,04</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,77</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,75</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7,67</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>8,04</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7,88</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>7,84</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,04</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,77</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7,67</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8,04</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7,88</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7,84</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>7,72</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 8,14</t>
+          <t>7,95; 8,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 8,04</t>
+          <t>7,81; 8,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,99</t>
+          <t>7,62; 7,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 7,9</t>
+          <t>7,64; 7,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,87</t>
+          <t>7,65; 7,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,82</t>
+          <t>7,51; 7,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,98; 8,11</t>
+          <t>7,99; 8,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 7,87</t>
+          <t>7,61; 7,83</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,27</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,31</t>
+          <t>7,36</t>
         </is>
       </c>
     </row>
@@ -861,37 +861,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,54</t>
+          <t>7,37; 7,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,62</t>
+          <t>7,43; 7,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,48</t>
+          <t>7,29; 7,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,68</t>
+          <t>7,51; 7,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,49</t>
+          <t>7,31; 7,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 7,63</t>
+          <t>7,45; 7,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,39</t>
+          <t>7,2; 7,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,49</t>
+          <t>7,37; 7,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 7,59</t>
+          <t>7,47; 7,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,4</t>
+          <t>7,27; 7,43</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,15</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,14</t>
         </is>
       </c>
     </row>
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,49</t>
+          <t>7,33; 7,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,33</t>
+          <t>7,14; 7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,41</t>
+          <t>7,26; 7,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,24</t>
+          <t>7,1; 7,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,37</t>
+          <t>7,21; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,22 +1036,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,48</t>
+          <t>7,37; 7,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,31</t>
+          <t>7,2; 7,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,37</t>
+          <t>7,25; 7,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,2</t>
+          <t>7,08; 7,2</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>7,02</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,49</t>
+          <t>7,3; 7,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,29</t>
+          <t>7,08; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,22; 7,4</t>
+          <t>7,22; 7,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 8,3</t>
+          <t>6,95; 7,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,06</t>
+          <t>6,85; 7,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,07</t>
+          <t>6,93; 7,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,15</t>
+          <t>6,99; 7,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,01</t>
+          <t>6,97; 7,07</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,5</t>
+          <t>7,27; 7,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,45</t>
+          <t>7,2; 7,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,24</t>
+          <t>7,02; 7,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 6,97</t>
+          <t>6,69; 6,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,02</t>
+          <t>6,75; 7,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,33</t>
+          <t>7,16; 7,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,12</t>
+          <t>6,93; 7,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,2</t>
+          <t>7,02; 7,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 6,92</t>
+          <t>6,81; 6,92</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,63</t>
+          <t>7,33; 7,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,49</t>
+          <t>7,14; 7,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,63</t>
+          <t>7,33; 7,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,03</t>
+          <t>6,84; 7,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,05</t>
+          <t>6,75; 7,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,05</t>
+          <t>6,76; 7,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,83; 7,13</t>
+          <t>6,85; 7,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 6,84</t>
+          <t>6,72; 6,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,27</t>
+          <t>7,07; 7,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,21</t>
+          <t>6,97; 7,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,32</t>
+          <t>7,12; 7,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 6,89</t>
+          <t>6,82; 6,94</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,91</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,57</t>
+          <t>7,21; 7,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,74</t>
+          <t>7,28; 7,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,79</t>
+          <t>7,47; 7,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,13</t>
+          <t>6,88; 7,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,21</t>
+          <t>6,85; 7,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 7,18</t>
+          <t>6,87; 7,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,33</t>
+          <t>7,02; 7,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 6,93</t>
+          <t>6,76; 6,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,29</t>
+          <t>7,04; 7,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,34</t>
+          <t>7,08; 7,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,48</t>
+          <t>7,23; 7,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 6,98</t>
+          <t>6,84; 6,99</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,11</t>
         </is>
       </c>
     </row>
@@ -1701,17 +1701,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,44</t>
+          <t>7,35; 7,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,51</t>
+          <t>7,43; 7,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,66</t>
+          <t>7,13; 7,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1721,37 +1721,37 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,23</t>
+          <t>7,14; 7,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,29</t>
+          <t>7,21; 7,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,05</t>
+          <t>7,01; 7,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,49</t>
+          <t>7,43; 7,49</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,32</t>
+          <t>7,26; 7,32</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,39</t>
+          <t>7,32; 7,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,36</t>
+          <t>7,08; 7,13</t>
         </is>
       </c>
     </row>
